--- a/_FACTORY/_LIGNES/_MAYENNE/B5_AUDIT/B5_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_MAYENNE/B5_AUDIT/B5_THEME.xlsx
@@ -900,10 +900,14 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -937,26 +941,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>
